--- a/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
@@ -174,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -314,11 +314,104 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -453,6 +546,21 @@
     </xf>
     <xf numFmtId="164" fontId="16" fillId="9" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -782,15 +890,6 @@
           <t>THORNFIELD LIFE SCIENCES MARKETING — Q4 2025 Managed Spend Export (Platform-Level, by Client)</t>
         </is>
       </c>
-      <c r="B1" s="18" t="n"/>
-      <c r="C1" s="18" t="n"/>
-      <c r="D1" s="18" t="n"/>
-      <c r="E1" s="18" t="n"/>
-      <c r="F1" s="18" t="n"/>
-      <c r="G1" s="18" t="n"/>
-      <c r="H1" s="18" t="n"/>
-      <c r="I1" s="18" t="n"/>
-      <c r="J1" s="18" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
@@ -798,19 +897,19 @@
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>Grace Feldman, Director, Analytics &amp; Reporting</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="21" t="n"/>
+      <c r="C2" s="49" t="n"/>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="49" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n"/>
+      <c r="H2" s="49" t="n"/>
+      <c r="I2" s="49" t="n"/>
+      <c r="J2" s="50" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -818,19 +917,12 @@
           <t>Source:</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="56" t="inlineStr">
         <is>
           <t>ERPNext (erp.thornfieldlsm.com) — Customer master joined to Sales Order line items, aggregated by billing month</t>
         </is>
       </c>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="23" t="n"/>
-      <c r="F3" s="23" t="n"/>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="23" t="n"/>
-      <c r="I3" s="23" t="n"/>
-      <c r="J3" s="24" t="n"/>
+      <c r="J3" s="51" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
@@ -838,19 +930,12 @@
           <t>Reporting basis:</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>Gross platform spend managed by Thornfield on behalf of client during the quarter (excludes management fee, reserve, and pass-through creative production).</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n"/>
-      <c r="D4" s="23" t="n"/>
-      <c r="E4" s="23" t="n"/>
-      <c r="F4" s="23" t="n"/>
-      <c r="G4" s="23" t="n"/>
-      <c r="H4" s="23" t="n"/>
-      <c r="I4" s="23" t="n"/>
-      <c r="J4" s="24" t="n"/>
+      <c r="J4" s="51" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
@@ -858,19 +943,12 @@
           <t>Data as of:</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>01/06/2026 (Q4 2025 books closed 12/31/2025)</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="23" t="n"/>
-      <c r="H5" s="23" t="n"/>
-      <c r="I5" s="23" t="n"/>
-      <c r="J5" s="24" t="n"/>
+      <c r="J5" s="51" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
@@ -878,19 +956,19 @@
           <t>Currency:</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>USD, format $#,##0</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="26" t="n"/>
-      <c r="E6" s="26" t="n"/>
-      <c r="F6" s="26" t="n"/>
-      <c r="G6" s="26" t="n"/>
-      <c r="H6" s="26" t="n"/>
-      <c r="I6" s="26" t="n"/>
-      <c r="J6" s="27" t="n"/>
+      <c r="C6" s="52" t="n"/>
+      <c r="D6" s="52" t="n"/>
+      <c r="E6" s="52" t="n"/>
+      <c r="F6" s="52" t="n"/>
+      <c r="G6" s="52" t="n"/>
+      <c r="H6" s="52" t="n"/>
+      <c r="I6" s="52" t="n"/>
+      <c r="J6" s="53" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1"/>
     <row r="8" ht="32" customHeight="1">
@@ -3470,7 +3548,7 @@
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D69" s="34" t="inlineStr">
@@ -3602,7 +3680,7 @@
       </c>
       <c r="C72" s="40" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D72" s="45" t="inlineStr">
@@ -3774,7 +3852,7 @@
       </c>
       <c r="C76" s="40" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D76" s="45" t="inlineStr">
@@ -3906,7 +3984,7 @@
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D79" s="46" t="inlineStr">
@@ -3994,7 +4072,7 @@
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D81" s="34" t="inlineStr">
@@ -4082,7 +4160,7 @@
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D83" s="46" t="inlineStr">
@@ -4170,7 +4248,7 @@
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
       <c r="D85" s="34" t="inlineStr">
@@ -4554,25 +4632,29 @@
       </c>
     </row>
     <row r="94" ht="28" customHeight="1">
-      <c r="A94" s="47" t="inlineStr">
+      <c r="A94" s="57" t="inlineStr">
         <is>
           <t>TOTALS (85 clients)</t>
         </is>
       </c>
-      <c r="B94" s="47" t="n"/>
-      <c r="C94" s="47" t="n"/>
-      <c r="D94" s="47" t="n"/>
-      <c r="E94" s="48" t="n">
-        <v>2815200</v>
-      </c>
-      <c r="F94" s="48" t="n">
-        <v>2851600</v>
-      </c>
-      <c r="G94" s="48" t="n">
-        <v>2853600</v>
-      </c>
-      <c r="H94" s="48" t="n">
-        <v>8520400</v>
+      <c r="B94" s="54" t="n"/>
+      <c r="C94" s="54" t="n"/>
+      <c r="D94" s="54" t="n"/>
+      <c r="E94" s="48">
+        <f>SUM(E9:E93)</f>
+        <v>2816000</v>
+      </c>
+      <c r="F94" s="48">
+        <f>SUM(F9:F93)</f>
+        <v>2854100</v>
+      </c>
+      <c r="G94" s="48">
+        <f>SUM(G9:G93)</f>
+        <v>2857900</v>
+      </c>
+      <c r="H94" s="48">
+        <f>SUM(H9:H93)</f>
+        <v>8528000</v>
       </c>
       <c r="I94" s="47" t="n"/>
       <c r="J94" s="47" t="n"/>

--- a/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
@@ -3575,7 +3575,7 @@
       </c>
       <c r="J69" s="37" t="inlineStr">
         <is>
-          <t>inherited account</t>
+          <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="J72" s="44" t="inlineStr">
         <is>
-          <t>inherited account</t>
+          <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J76" s="44" t="inlineStr">
         <is>
-          <t>inherited account; regulated client</t>
+          <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="J79" s="37" t="inlineStr">
         <is>
-          <t>inherited account; regulated client</t>
+          <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="J81" s="37" t="inlineStr">
         <is>
-          <t>inherited account</t>
+          <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="J83" s="37" t="inlineStr">
         <is>
-          <t>inherited account; regulated client</t>
+          <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="J85" s="37" t="inlineStr">
         <is>
-          <t>inherited account</t>
+          <t>Thornfield-native account</t>
         </is>
       </c>
     </row>

--- a/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +116,11 @@
       <b val="1"/>
       <color rgb="000F172A"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF334155"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="10">
@@ -411,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -561,6 +566,12 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,7 +1050,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1079,7 +1090,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1119,7 +1130,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1159,7 +1170,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1199,7 +1210,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D13" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1283,7 +1294,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D15" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1323,7 +1334,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D16" s="41" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1363,7 +1374,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="D17" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1403,7 +1414,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D18" s="41" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1483,7 +1494,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D20" s="41" t="inlineStr">
+      <c r="D20" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1571,7 +1582,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D22" s="41" t="inlineStr">
+      <c r="D22" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1611,7 +1622,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D23" s="34" t="inlineStr">
+      <c r="D23" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1691,7 +1702,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="D25" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1775,7 +1786,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D27" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1899,7 +1910,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D30" s="41" t="inlineStr">
+      <c r="D30" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1939,7 +1950,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D31" s="34" t="inlineStr">
+      <c r="D31" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2067,7 +2078,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D34" s="41" t="inlineStr">
+      <c r="D34" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2107,7 +2118,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="D35" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2147,7 +2158,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D36" s="41" t="inlineStr">
+      <c r="D36" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2231,7 +2242,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D38" s="41" t="inlineStr">
+      <c r="D38" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2271,7 +2282,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D39" s="34" t="inlineStr">
+      <c r="D39" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2355,7 +2366,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D41" s="34" t="inlineStr">
+      <c r="D41" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2395,7 +2406,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D42" s="41" t="inlineStr">
+      <c r="D42" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2435,7 +2446,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D43" s="34" t="inlineStr">
+      <c r="D43" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2475,7 +2486,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D44" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2515,7 +2526,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D45" s="34" t="inlineStr">
+      <c r="D45" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2555,7 +2566,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D46" s="41" t="inlineStr">
+      <c r="D46" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2639,7 +2650,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D48" s="41" t="inlineStr">
+      <c r="D48" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2679,7 +2690,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D49" s="34" t="inlineStr">
+      <c r="D49" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2719,7 +2730,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D50" s="41" t="inlineStr">
+      <c r="D50" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2759,7 +2770,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D51" s="34" t="inlineStr">
+      <c r="D51" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2847,7 +2858,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D53" s="34" t="inlineStr">
+      <c r="D53" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2891,7 +2902,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D54" s="41" t="inlineStr">
+      <c r="D54" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2935,7 +2946,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D55" s="34" t="inlineStr">
+      <c r="D55" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2979,7 +2990,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D56" s="41" t="inlineStr">
+      <c r="D56" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3023,7 +3034,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D57" s="34" t="inlineStr">
+      <c r="D57" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3111,7 +3122,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D59" s="34" t="inlineStr">
+      <c r="D59" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3155,7 +3166,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D60" s="41" t="inlineStr">
+      <c r="D60" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3199,7 +3210,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D61" s="34" t="inlineStr">
+      <c r="D61" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3375,7 +3386,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D65" s="34" t="inlineStr">
+      <c r="D65" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3463,7 +3474,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D67" s="34" t="inlineStr">
+      <c r="D67" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3551,7 +3562,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D69" s="34" t="inlineStr">
+      <c r="D69" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3639,7 +3650,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D71" s="34" t="inlineStr">
+      <c r="D71" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3727,7 +3738,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D73" s="34" t="inlineStr">
+      <c r="D73" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3771,7 +3782,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D74" s="41" t="inlineStr">
+      <c r="D74" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3815,7 +3826,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D75" s="34" t="inlineStr">
+      <c r="D75" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3899,7 +3910,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D77" s="34" t="inlineStr">
+      <c r="D77" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3943,7 +3954,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D78" s="41" t="inlineStr">
+      <c r="D78" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4031,7 +4042,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D80" s="41" t="inlineStr">
+      <c r="D80" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4075,7 +4086,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D81" s="34" t="inlineStr">
+      <c r="D81" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4119,7 +4130,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D82" s="41" t="inlineStr">
+      <c r="D82" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4207,7 +4218,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D84" s="41" t="inlineStr">
+      <c r="D84" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4251,7 +4262,7 @@
           <t>Thornfield native</t>
         </is>
       </c>
-      <c r="D85" s="34" t="inlineStr">
+      <c r="D85" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4295,7 +4306,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D86" s="41" t="inlineStr">
+      <c r="D86" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4383,7 +4394,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D88" s="41" t="inlineStr">
+      <c r="D88" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4427,7 +4438,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D89" s="34" t="inlineStr">
+      <c r="D89" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4471,7 +4482,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D90" s="41" t="inlineStr">
+      <c r="D90" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4559,7 +4570,7 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="D92" s="41" t="inlineStr">
+      <c r="D92" s="59" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>Meridian Biosystems</t>
+          <t>Thistlewood Biosystems</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">

--- a/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q4_2025_managed_spend_export.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,6 +120,17 @@
     <font>
       <name val="Segoe UI"/>
       <color rgb="FF334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF475569"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -416,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -572,6 +583,18 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1035,7 +1058,7 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0004</t>
         </is>
@@ -1075,7 +1098,7 @@
       <c r="J9" s="37" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0006</t>
         </is>
@@ -1115,7 +1138,7 @@
       <c r="J10" s="44" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0007</t>
         </is>
@@ -1155,7 +1178,7 @@
       <c r="J11" s="37" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0011</t>
         </is>
@@ -1195,7 +1218,7 @@
       <c r="J12" s="44" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0014</t>
         </is>
@@ -1235,7 +1258,7 @@
       <c r="J13" s="37" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0016</t>
         </is>
@@ -1272,14 +1295,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J14" s="44" t="inlineStr">
+      <c r="J14" s="62" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0019</t>
         </is>
@@ -1319,7 +1342,7 @@
       <c r="J15" s="37" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0022</t>
         </is>
@@ -1359,7 +1382,7 @@
       <c r="J16" s="44" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0025</t>
         </is>
@@ -1399,7 +1422,7 @@
       <c r="J17" s="37" t="inlineStr"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0028</t>
         </is>
@@ -1439,7 +1462,7 @@
       <c r="J18" s="44" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0031</t>
         </is>
@@ -1479,7 +1502,7 @@
       <c r="J19" s="37" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0033</t>
         </is>
@@ -1516,14 +1539,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J20" s="44" t="inlineStr">
+      <c r="J20" s="62" t="inlineStr">
         <is>
           <t>Platform-level media spend; distinct from billed service fees. Q4 media placement includes November paid-social burst.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0037</t>
         </is>
@@ -1560,14 +1583,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J21" s="37" t="inlineStr">
+      <c r="J21" s="63" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0041</t>
         </is>
@@ -1607,7 +1630,7 @@
       <c r="J22" s="44" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0044</t>
         </is>
@@ -1647,7 +1670,7 @@
       <c r="J23" s="37" t="inlineStr"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0047</t>
         </is>
@@ -1687,7 +1710,7 @@
       <c r="J24" s="44" t="inlineStr"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0049</t>
         </is>
@@ -1727,7 +1750,7 @@
       <c r="J25" s="37" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0052</t>
         </is>
@@ -1764,14 +1787,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J26" s="44" t="inlineStr">
+      <c r="J26" s="62" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0056</t>
         </is>
@@ -1811,7 +1834,7 @@
       <c r="J27" s="37" t="inlineStr"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0059</t>
         </is>
@@ -1851,7 +1874,7 @@
       <c r="J28" s="44" t="inlineStr"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0063</t>
         </is>
@@ -1888,14 +1911,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J29" s="37" t="inlineStr">
+      <c r="J29" s="63" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="38" t="inlineStr">
+      <c r="A30" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0066</t>
         </is>
@@ -1935,7 +1958,7 @@
       <c r="J30" s="44" t="inlineStr"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0069</t>
         </is>
@@ -1975,7 +1998,7 @@
       <c r="J31" s="37" t="inlineStr"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="38" t="inlineStr">
+      <c r="A32" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0072</t>
         </is>
@@ -2012,14 +2035,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J32" s="44" t="inlineStr">
+      <c r="J32" s="62" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0075</t>
         </is>
@@ -2056,14 +2079,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J33" s="37" t="inlineStr">
+      <c r="J33" s="63" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="38" t="inlineStr">
+      <c r="A34" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0078</t>
         </is>
@@ -2103,7 +2126,7 @@
       <c r="J34" s="44" t="inlineStr"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0081</t>
         </is>
@@ -2143,7 +2166,7 @@
       <c r="J35" s="37" t="inlineStr"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="38" t="inlineStr">
+      <c r="A36" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0084</t>
         </is>
@@ -2183,7 +2206,7 @@
       <c r="J36" s="44" t="inlineStr"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0088</t>
         </is>
@@ -2220,14 +2243,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J37" s="37" t="inlineStr">
+      <c r="J37" s="63" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="38" t="inlineStr">
+      <c r="A38" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0091</t>
         </is>
@@ -2267,7 +2290,7 @@
       <c r="J38" s="44" t="inlineStr"/>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0094</t>
         </is>
@@ -2307,7 +2330,7 @@
       <c r="J39" s="37" t="inlineStr"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="A40" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0097</t>
         </is>
@@ -2344,14 +2367,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J40" s="44" t="inlineStr">
+      <c r="J40" s="62" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0100</t>
         </is>
@@ -2391,7 +2414,7 @@
       <c r="J41" s="37" t="inlineStr"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="38" t="inlineStr">
+      <c r="A42" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0103</t>
         </is>
@@ -2431,7 +2454,7 @@
       <c r="J42" s="44" t="inlineStr"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="31" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0106</t>
         </is>
@@ -2471,7 +2494,7 @@
       <c r="J43" s="37" t="inlineStr"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="38" t="inlineStr">
+      <c r="A44" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0109</t>
         </is>
@@ -2511,7 +2534,7 @@
       <c r="J44" s="44" t="inlineStr"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="31" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0112</t>
         </is>
@@ -2551,7 +2574,7 @@
       <c r="J45" s="37" t="inlineStr"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="38" t="inlineStr">
+      <c r="A46" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0115</t>
         </is>
@@ -2591,7 +2614,7 @@
       <c r="J46" s="44" t="inlineStr"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="31" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0118</t>
         </is>
@@ -2628,14 +2651,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J47" s="37" t="inlineStr">
+      <c r="J47" s="63" t="inlineStr">
         <is>
           <t>regulated client</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="38" t="inlineStr">
+      <c r="A48" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0121</t>
         </is>
@@ -2675,7 +2698,7 @@
       <c r="J48" s="44" t="inlineStr"/>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="A49" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0124</t>
         </is>
@@ -2715,7 +2738,7 @@
       <c r="J49" s="37" t="inlineStr"/>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="38" t="inlineStr">
+      <c r="A50" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0127</t>
         </is>
@@ -2755,7 +2778,7 @@
       <c r="J50" s="44" t="inlineStr"/>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="A51" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0130</t>
         </is>
@@ -2792,14 +2815,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J51" s="37" t="inlineStr">
+      <c r="J51" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="38" t="inlineStr">
+      <c r="A52" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0133</t>
         </is>
@@ -2836,14 +2859,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J52" s="44" t="inlineStr">
+      <c r="J52" s="62" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="31" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0136</t>
         </is>
@@ -2880,14 +2903,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J53" s="37" t="inlineStr">
+      <c r="J53" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="38" t="inlineStr">
+      <c r="A54" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0139</t>
         </is>
@@ -2924,14 +2947,14 @@
           <t>Trade Publications</t>
         </is>
       </c>
-      <c r="J54" s="44" t="inlineStr">
+      <c r="J54" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="31" t="inlineStr">
+      <c r="A55" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0142</t>
         </is>
@@ -2968,14 +2991,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J55" s="37" t="inlineStr">
+      <c r="J55" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="38" t="inlineStr">
+      <c r="A56" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0145</t>
         </is>
@@ -3012,14 +3035,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J56" s="44" t="inlineStr">
+      <c r="J56" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="31" t="inlineStr">
+      <c r="A57" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0148</t>
         </is>
@@ -3056,14 +3079,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J57" s="37" t="inlineStr">
+      <c r="J57" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="38" t="inlineStr">
+      <c r="A58" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0151</t>
         </is>
@@ -3100,14 +3123,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J58" s="44" t="inlineStr">
+      <c r="J58" s="62" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="31" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0154</t>
         </is>
@@ -3144,14 +3167,14 @@
           <t>Trade Publications</t>
         </is>
       </c>
-      <c r="J59" s="37" t="inlineStr">
+      <c r="J59" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="38" t="inlineStr">
+      <c r="A60" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0157</t>
         </is>
@@ -3188,14 +3211,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J60" s="44" t="inlineStr">
+      <c r="J60" s="62" t="inlineStr">
         <is>
           <t>inherited account; renewal 12/05/2025</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="31" t="inlineStr">
+      <c r="A61" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0160</t>
         </is>
@@ -3232,14 +3255,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J61" s="37" t="inlineStr">
+      <c r="J61" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="38" t="inlineStr">
+      <c r="A62" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0163</t>
         </is>
@@ -3276,14 +3299,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J62" s="44" t="inlineStr">
+      <c r="J62" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="31" t="inlineStr">
+      <c r="A63" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0166</t>
         </is>
@@ -3320,14 +3343,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J63" s="37" t="inlineStr">
+      <c r="J63" s="63" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="38" t="inlineStr">
+      <c r="A64" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0169</t>
         </is>
@@ -3364,14 +3387,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J64" s="44" t="inlineStr">
+      <c r="J64" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="31" t="inlineStr">
+      <c r="A65" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0172</t>
         </is>
@@ -3408,14 +3431,14 @@
           <t>Trade Publications</t>
         </is>
       </c>
-      <c r="J65" s="37" t="inlineStr">
+      <c r="J65" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="38" t="inlineStr">
+      <c r="A66" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0175</t>
         </is>
@@ -3452,14 +3475,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J66" s="44" t="inlineStr">
+      <c r="J66" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="31" t="inlineStr">
+      <c r="A67" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0178</t>
         </is>
@@ -3496,14 +3519,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J67" s="37" t="inlineStr">
+      <c r="J67" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="38" t="inlineStr">
+      <c r="A68" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0181</t>
         </is>
@@ -3540,14 +3563,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J68" s="44" t="inlineStr">
+      <c r="J68" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="31" t="inlineStr">
+      <c r="A69" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0184</t>
         </is>
@@ -3584,14 +3607,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J69" s="37" t="inlineStr">
+      <c r="J69" s="63" t="inlineStr">
         <is>
           <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="38" t="inlineStr">
+      <c r="A70" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0187</t>
         </is>
@@ -3628,14 +3651,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J70" s="44" t="inlineStr">
+      <c r="J70" s="62" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="31" t="inlineStr">
+      <c r="A71" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0190</t>
         </is>
@@ -3672,14 +3695,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J71" s="37" t="inlineStr">
+      <c r="J71" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="38" t="inlineStr">
+      <c r="A72" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0193</t>
         </is>
@@ -3716,14 +3739,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J72" s="44" t="inlineStr">
+      <c r="J72" s="62" t="inlineStr">
         <is>
           <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="31" t="inlineStr">
+      <c r="A73" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0196</t>
         </is>
@@ -3760,14 +3783,14 @@
           <t>Trade Publications</t>
         </is>
       </c>
-      <c r="J73" s="37" t="inlineStr">
+      <c r="J73" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="38" t="inlineStr">
+      <c r="A74" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0198</t>
         </is>
@@ -3804,14 +3827,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J74" s="44" t="inlineStr">
+      <c r="J74" s="62" t="inlineStr">
         <is>
           <t>inherited account; retainer billed separately</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="31" t="inlineStr">
+      <c r="A75" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0201</t>
         </is>
@@ -3851,7 +3874,7 @@
       <c r="J75" s="37" t="inlineStr"/>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="38" t="inlineStr">
+      <c r="A76" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0204</t>
         </is>
@@ -3888,14 +3911,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J76" s="44" t="inlineStr">
+      <c r="J76" s="62" t="inlineStr">
         <is>
           <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="31" t="inlineStr">
+      <c r="A77" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0207</t>
         </is>
@@ -3932,14 +3955,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J77" s="37" t="inlineStr">
+      <c r="J77" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="38" t="inlineStr">
+      <c r="A78" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0210</t>
         </is>
@@ -3976,14 +3999,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J78" s="44" t="inlineStr">
+      <c r="J78" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="31" t="inlineStr">
+      <c r="A79" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0213</t>
         </is>
@@ -4020,14 +4043,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J79" s="37" t="inlineStr">
+      <c r="J79" s="63" t="inlineStr">
         <is>
           <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="38" t="inlineStr">
+      <c r="A80" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0216</t>
         </is>
@@ -4064,14 +4087,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J80" s="44" t="inlineStr">
+      <c r="J80" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="31" t="inlineStr">
+      <c r="A81" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0219</t>
         </is>
@@ -4108,14 +4131,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J81" s="37" t="inlineStr">
+      <c r="J81" s="63" t="inlineStr">
         <is>
           <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="38" t="inlineStr">
+      <c r="A82" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0222</t>
         </is>
@@ -4152,14 +4175,14 @@
           <t>Trade Publications</t>
         </is>
       </c>
-      <c r="J82" s="44" t="inlineStr">
+      <c r="J82" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="31" t="inlineStr">
+      <c r="A83" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0225</t>
         </is>
@@ -4196,14 +4219,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J83" s="37" t="inlineStr">
+      <c r="J83" s="63" t="inlineStr">
         <is>
           <t>Thornfield-native account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="38" t="inlineStr">
+      <c r="A84" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0228</t>
         </is>
@@ -4240,14 +4263,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J84" s="44" t="inlineStr">
+      <c r="J84" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="31" t="inlineStr">
+      <c r="A85" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0231</t>
         </is>
@@ -4284,14 +4307,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J85" s="37" t="inlineStr">
+      <c r="J85" s="63" t="inlineStr">
         <is>
           <t>Thornfield-native account</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="38" t="inlineStr">
+      <c r="A86" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0234</t>
         </is>
@@ -4328,14 +4351,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J86" s="44" t="inlineStr">
+      <c r="J86" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="31" t="inlineStr">
+      <c r="A87" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0237</t>
         </is>
@@ -4372,14 +4395,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J87" s="37" t="inlineStr">
+      <c r="J87" s="63" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="38" t="inlineStr">
+      <c r="A88" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0240</t>
         </is>
@@ -4416,14 +4439,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J88" s="44" t="inlineStr">
+      <c r="J88" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="31" t="inlineStr">
+      <c r="A89" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0243</t>
         </is>
@@ -4460,14 +4483,14 @@
           <t>Trade Publications</t>
         </is>
       </c>
-      <c r="J89" s="37" t="inlineStr">
+      <c r="J89" s="63" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="38" t="inlineStr">
+      <c r="A90" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0246</t>
         </is>
@@ -4504,14 +4527,14 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J90" s="44" t="inlineStr">
+      <c r="J90" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="31" t="inlineStr">
+      <c r="A91" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0249</t>
         </is>
@@ -4548,14 +4571,14 @@
           <t>Google Ads</t>
         </is>
       </c>
-      <c r="J91" s="37" t="inlineStr">
+      <c r="J91" s="63" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="38" t="inlineStr">
+      <c r="A92" s="61" t="inlineStr">
         <is>
           <t>CUST-2025-0252</t>
         </is>
@@ -4592,14 +4615,14 @@
           <t>Programmatic Display</t>
         </is>
       </c>
-      <c r="J92" s="44" t="inlineStr">
+      <c r="J92" s="62" t="inlineStr">
         <is>
           <t>inherited account</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="31" t="inlineStr">
+      <c r="A93" s="60" t="inlineStr">
         <is>
           <t>CUST-2025-0255</t>
         </is>
@@ -4636,7 +4659,7 @@
           <t>LinkedIn Ads</t>
         </is>
       </c>
-      <c r="J93" s="37" t="inlineStr">
+      <c r="J93" s="63" t="inlineStr">
         <is>
           <t>inherited account; regulated client</t>
         </is>
